--- a/光伏配储项目/电价数据/2026/扬帆站.xlsx
+++ b/光伏配储项目/电价数据/2026/扬帆站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33432</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.10274</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.40179</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.41873</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26517</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.25344</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.25716</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.27587</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07226</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.25492</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.16996</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25588</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24054</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.21461</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.27686</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.7514700000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.7108300000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.9778</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.78369</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.45397</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.5156900000000001</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.53728</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.84626</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.35161</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.6161599999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.75043</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.57257</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.64776</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.03492</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.1379</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.65267</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.26035</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.16878</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.09751</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.68726</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.61949</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.5943200000000001</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.51606</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.53215</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.81959</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.09714</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.16228</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4741</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.50131</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.48647</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.48446</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.46255</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.44676</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44913</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.40477</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.43144</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6474500000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.60885</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.7319199999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.54688</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.47632</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5966</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.82961</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5718799999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.67671</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.68645</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.54514</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.63642</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.01031</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.61073</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.3621</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.59551</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7359</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.30284</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.03642</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.4065</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.24491</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.52921</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.05165</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>1.03548</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>1.02607</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42847</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.48384</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4665</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4837</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.42857</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.42511</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.43346</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.42276</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.15614</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.19873</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26627</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.11126</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.68177</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.57965</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.57033</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.79704</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.79704</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.73319</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.8145800000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.9203300000000001</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.00201</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.02477</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.0947</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.50131</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.51781</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.72566</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.76524</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.61312</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.5923999999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.48984</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.57963</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45817</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5114300000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5218200000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.58456</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.62717</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5941000000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.63978</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.9955499999999999</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.5806699999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.7082999999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51159</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57076</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.63237</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.70661</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.7495700000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.43376</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6188400000000001</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.47978</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.52973</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.67848</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.53055</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.68383</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.59285</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.58208</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5368200000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.72894</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.42766</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.44223</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.60987</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.58097</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.49348</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.4117</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.5027699999999999</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.40506</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.41515</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.46658</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44612</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.45665</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.48318</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48466</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.15638</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.80629</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.41838</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.14762</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.42294</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.50751</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.67199</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.42968</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50242</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.27442</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14359</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02753</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26442</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25745</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23904</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10382</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26644</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03953</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26353</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.43602</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31947</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25893</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.21795</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.20089</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.24167</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.13754</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25588</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.0369</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.16125</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25368</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.2229</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.20134</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.23401</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.18401</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25512</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27587</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.21063</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.27038</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10709</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04621</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01023</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20662</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04947</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27602</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19556</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01342</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06075999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05897</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31708</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.23601</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.43682</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78343</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8704400000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.66226</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57531</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44386</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.40059</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44414</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.45376</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.52058</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.59365</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8284400000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44913</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.48905</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.70586</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.75571</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26821</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.43537</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18842</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26557</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26559</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32552</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.38655</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.24233</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.24749</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.26493</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.18226</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.21051</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.24596</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.17581</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.25876</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.28049</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.24189</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.26716</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.19477</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.17631</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.17079</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.15762</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.14212</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.17183</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.07646</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.16779</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.00259</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.12625</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.13509</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.10234</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.13296</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.26076</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.26503</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.21843</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.26196</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.24793</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.26302</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.26459</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.23629</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.25459</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.25848</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.25771</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.24177</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.26216</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.26565</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.27625</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.27195</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.26773</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.26615</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.25327</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.28544</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.26684</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.26209</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.27199</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.12627</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.49151</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.0603</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.5914400000000001</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.53934</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.14094</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.13043</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.2656</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.27036</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.28169</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.27802</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.26457</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.11325</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.17546</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.16644</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.27137</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.14848</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.22382</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.27413</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.12576</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.23435</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.26379</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.21459</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.16993</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.2758</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26043</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.16476</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.19672</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.25054</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.17087</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.19705</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.24794</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.24947</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.25914</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.28986</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.53938</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.28773</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.24632</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.22132</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.25201</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.23335</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.22543</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.14512</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.17601</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19658</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.16858</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.19369</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.14469</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.21205</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.23107</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.2289</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.26221</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.25862</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.07890000000000001</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.08401</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.18631</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.19691</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.2545</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.02479</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.20094</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.02582</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.13732</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.13467</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.17171</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.24426</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.25505</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.16227</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.15021</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.27439</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.11921</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.25035</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.09351999999999999</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.16646</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.25328</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.23747</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.26567</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.26042</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.2547</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.25131</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.24063</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.24615</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.26127</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.27272</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26311</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.26472</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.25729</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.26767</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.26826</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28943</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.5111600000000001</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25572</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28576</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.41655</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29859</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29355</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28584</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.49122</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.44446</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.46042</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.60749</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.42535</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.44295</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.31845</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29621</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.5405</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.55653</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.16177</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.49365</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.73695</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49567</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.46171</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.63164</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.7673300000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.50026</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.60199</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.92532</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27888</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.53371</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.42679</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.41895</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.17277</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.45289</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.61948</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.5770700000000001</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.56199</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.9168099999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.60222</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.58408</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.69345</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.5221699999999999</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.65338</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.44343</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.8352000000000001</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.65632</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.5949800000000001</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.8334600000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70343</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47895</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.18517</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.27177</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.23364</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28895</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.03731</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.17646</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20754</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.1994</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27557</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.2013</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19859</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16422</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.24041</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19832</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20397</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.17039</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.21125</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17792</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16892</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.20904</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.23292</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.27901</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.28572</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.25977</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.2794700000000001</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.27742</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.24939</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.26458</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.27261</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.23827</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.25591</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.26238</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.16816</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.27996</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.28023</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27883</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28909</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27925</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.26973</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.23725</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.16288</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.13576</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.24135</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32087</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.00627</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28758</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27704</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27738</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28779</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.51091</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.98014</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.9743200000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.21651</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29959</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28926</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.51068</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.42512</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.67924</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.06576</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.97949</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.06509</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.27591</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.5974700000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.5165</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.73793</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.54199</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.6789400000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31713</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45312</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.47742</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.43029</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.5662</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.6323</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.7097599999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.58357</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67338</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.18356</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.49668</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.26089</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.45455</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.40535</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.08721</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.8169299999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64446</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32592</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27844</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28871</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.28288</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.64701</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.43023</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.19088</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.26575</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.18278</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.17964</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.19687</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.24091</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.22303</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.18754</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.26038</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.16281</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.28985</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.13097</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.16991</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.16176</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.17311</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.18066</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.28958</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.25526</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.23003</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.22422</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.02037</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.26266</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.01661</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17851</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.00609</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20916</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17733</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.01501</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16738</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.17217</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.20494</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16967</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.17252</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17537</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.01385</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17823</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.01366</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.18967</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.19033</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15949</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.02286</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.23011</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.25099</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.13831</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.26617</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.21435</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00326</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2563</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25224</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.28719</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.25826</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.26898</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.26181</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.28066</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.27386</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.26311</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22909</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.19939</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.19257</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25436</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.25447</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.16934</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.17789</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.25469</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.15587</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.27126</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.15015</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.20965</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.23449</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.27377</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28499</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.05905</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.19305</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18997</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26978</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.00632</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20876</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22062</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.04859</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.00435</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.008569999999999999</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.00856</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20348</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.00496</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.00797</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.1842</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.00433</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.00434</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.009689999999999999</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24632</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04237</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00567</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02201</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02065</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02935</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04405</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.01003</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.26564</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04937</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03879999999999999</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18128</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.25363</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.27237</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.26869</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.009269999999999999</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28347</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27435</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.04578</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.18185</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17618</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.18069</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17792</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.01081</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.17386</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16218</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.009679999999999999</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.04087</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.03842</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.00911</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.01752</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.02006</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.02456</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20661</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28169</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.01254</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.24669</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8595</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8615499999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09387999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.00793</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.44085</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00219</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00152</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06863</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47488</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.13988</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.7513099999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.47211</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.55364</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.31234</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.44285</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.49313</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.89574</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.5954199999999999</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.22259</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.22082</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.22903</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.4051</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.47882</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.5995499999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.49786</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31223</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.5907100000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.27308</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.20439</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26499</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.26063</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25364</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.2236</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.27525</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.21177</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17916</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.17337</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17618</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.01131</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.1729</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.19472</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.24278</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25091</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25828</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25843</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.2961</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29765</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.8440299999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.55192</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29679</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.57404</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.5781799999999999</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.20898</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.291</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.48464</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.70251</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.07313</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.27621</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.50598</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.07564</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.4666</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43012</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20425</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.32013</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47452</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.40363</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.8905299999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.9807899999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.59357</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.04986</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.63208</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.79412</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.16668</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.95927</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.6455299999999999</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.56926</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.3644</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.30218</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.09655</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.88722</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.50893</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32471</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28557</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.01165</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.27554</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.43687</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.58329</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20113</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43609</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.55714</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.7564299999999999</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.41691</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.7273500000000001</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.5509299999999999</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.7413</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.08634</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.5399299999999999</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.7776799999999999</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.57374</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.6287</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.329</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.11203</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.48647</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.6167100000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.53989</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.51788</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.43201</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.48295</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.6080800000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.6519299999999999</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.90539</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.6173200000000001</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.42639</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.53063</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.5913999999999999</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33992</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30464</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14573</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19862</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14601</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28761</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04754</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12155</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22595</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26025</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14406</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14523</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26977</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15772</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20123</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.25351</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36973</v>
       </c>
     </row>
   </sheetData>
